--- a/CATALOGO_COMPLEMENTARIA.xlsx
+++ b/CATALOGO_COMPLEMENTARIA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yeisonc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF648AB-C62B-4600-BFA4-6EAA7E34DD2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9596FD05-BE76-4258-B754-353485306E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{078C0FF7-D1FA-4BFF-9C6C-84C2489BFC64}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7577" uniqueCount="3267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7607" uniqueCount="3279">
   <si>
     <t>NIVEL_FORMACION</t>
   </si>
@@ -9837,6 +9837,42 @@
   </si>
   <si>
     <t>Profesionales de la salud, la higiene laboral y ambiental</t>
+  </si>
+  <si>
+    <t>COMERCIALIZACION EN MERCADOS CAMPESINOS</t>
+  </si>
+  <si>
+    <t>SEGURIDAD Y SALUD EN EL TRABAJO EN CONTEXTOS RURALES</t>
+  </si>
+  <si>
+    <t>HERRAMIENTAS DE GESTION Y SOSTENIBILIDAD EN MUSEOS</t>
+  </si>
+  <si>
+    <t>CREACION DE CONTENIDOS DIDACTICOS CON INTELIGENCIA ARTIFICIAL</t>
+  </si>
+  <si>
+    <t>MERCADEO Y VENTAS.</t>
+  </si>
+  <si>
+    <t>66120038</t>
+  </si>
+  <si>
+    <t>22620504</t>
+  </si>
+  <si>
+    <t>52110000</t>
+  </si>
+  <si>
+    <t>41311658</t>
+  </si>
+  <si>
+    <t>63110195</t>
+  </si>
+  <si>
+    <t>63550055</t>
+  </si>
+  <si>
+    <t>Ocupaciones Técnicas Relacionadas con Museos y Galerías</t>
   </si>
 </sst>
 </file>
@@ -10776,7 +10812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25169BF6-E4C9-4119-B12D-AB0CA65D0423}">
-  <dimension ref="A1:G4064"/>
+  <dimension ref="A1:G4033"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -45632,27 +45668,159 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="1516" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1517" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1518" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1519" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1520" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1521" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1522" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1523" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1524" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1525" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1526" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1527" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1528" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1529" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1530" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1531" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1532" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1533" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1534" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1535" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1536" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1516" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1516" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1516" s="5" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C1516">
+        <v>1</v>
+      </c>
+      <c r="D1516" t="s">
+        <v>3267</v>
+      </c>
+      <c r="E1516">
+        <v>48</v>
+      </c>
+      <c r="F1516" s="3" t="s">
+        <v>3029</v>
+      </c>
+      <c r="G1516" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1517" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1517" s="5" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C1517">
+        <v>1</v>
+      </c>
+      <c r="D1517" t="s">
+        <v>3268</v>
+      </c>
+      <c r="E1517">
+        <v>48</v>
+      </c>
+      <c r="F1517" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G1517" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1518" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1518" s="5" t="s">
+        <v>3274</v>
+      </c>
+      <c r="C1518">
+        <v>1</v>
+      </c>
+      <c r="D1518" t="s">
+        <v>3269</v>
+      </c>
+      <c r="E1518">
+        <v>48</v>
+      </c>
+      <c r="F1518" s="3" t="s">
+        <v>3278</v>
+      </c>
+      <c r="G1518" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1519" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1519" s="5" t="s">
+        <v>3275</v>
+      </c>
+      <c r="C1519">
+        <v>1</v>
+      </c>
+      <c r="D1519" t="s">
+        <v>3270</v>
+      </c>
+      <c r="E1519">
+        <v>48</v>
+      </c>
+      <c r="F1519" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="G1519" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1520" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1520" s="5" t="s">
+        <v>3276</v>
+      </c>
+      <c r="C1520">
+        <v>1</v>
+      </c>
+      <c r="D1520" t="s">
+        <v>3271</v>
+      </c>
+      <c r="E1520">
+        <v>48</v>
+      </c>
+      <c r="F1520" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G1520" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1521" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1521" s="5" t="s">
+        <v>3277</v>
+      </c>
+      <c r="C1521">
+        <v>2</v>
+      </c>
+      <c r="D1521" t="s">
+        <v>636</v>
+      </c>
+      <c r="E1521">
+        <v>96</v>
+      </c>
+      <c r="F1521" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="G1521" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1523" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1524" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1525" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1526" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1527" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1528" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1529" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1530" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1531" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1532" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1533" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1534" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1535" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1536" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1537" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1538" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1539" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -48150,40 +48318,9 @@
     <row r="4031" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4032" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4033" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4034" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4035" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4036" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4037" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4038" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4039" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4040" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4041" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4042" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4043" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4044" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4045" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4046" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4047" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4048" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4049" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4050" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4051" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4052" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4053" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4054" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4055" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4056" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4057" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4058" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4059" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4060" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4061" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4062" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4063" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4064" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/CATALOGO_COMPLEMENTARIA.xlsx
+++ b/CATALOGO_COMPLEMENTARIA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yeisonc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9596FD05-BE76-4258-B754-353485306E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77A54BA-15F3-4B5C-B75C-878F87343A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{078C0FF7-D1FA-4BFF-9C6C-84C2489BFC64}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7607" uniqueCount="3279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7647" uniqueCount="3296">
   <si>
     <t>NIVEL_FORMACION</t>
   </si>
@@ -9873,6 +9873,57 @@
   </si>
   <si>
     <t>Ocupaciones Técnicas Relacionadas con Museos y Galerías</t>
+  </si>
+  <si>
+    <t>HERRAMIENTAS DE INNOVACION PARA FORTALECER LA INVESTIGACION EN SALUD PUBLICA</t>
+  </si>
+  <si>
+    <t>CONOCIMIENTO DEL SISTEMA FERROVIARIO</t>
+  </si>
+  <si>
+    <t>OPTIMIZACION DEL SERVICIO AL CLIENTE EN EL CAMPO DE LA ESTETICA Y BELLEZA CON IA</t>
+  </si>
+  <si>
+    <t>PLANIFICACION DE ESTRATEGIAS DE MERCADO E INVERSION PARA EMPRENDIMIENTOS</t>
+  </si>
+  <si>
+    <t>APLICACION PEDAGOGICA DE LA IA EN LA FORMACION PROFESIONAL INTEGRAL</t>
+  </si>
+  <si>
+    <t>GLOBALIZACION ECONOMICA Y SU INCIDENCIA EN LOS DERECHOS</t>
+  </si>
+  <si>
+    <t>EL PROCESO DE LA VENTA.</t>
+  </si>
+  <si>
+    <t>VALIDACION DE PROTOTIPOS FUNCIONALES</t>
+  </si>
+  <si>
+    <t>41730056</t>
+  </si>
+  <si>
+    <t>22750000</t>
+  </si>
+  <si>
+    <t>51260002</t>
+  </si>
+  <si>
+    <t>11220158</t>
+  </si>
+  <si>
+    <t>41311652</t>
+  </si>
+  <si>
+    <t>41210049</t>
+  </si>
+  <si>
+    <t>62330165</t>
+  </si>
+  <si>
+    <t>11220157</t>
+  </si>
+  <si>
+    <t>Controladores de Tráfico Ferroviario y Marítimo</t>
   </si>
 </sst>
 </file>
@@ -10471,7 +10522,57 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -10812,7 +10913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25169BF6-E4C9-4119-B12D-AB0CA65D0423}">
-  <dimension ref="A1:G4033"/>
+  <dimension ref="A1:G4029"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -45806,16 +45907,196 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="1522" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1523" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1524" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1525" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1526" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1527" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1528" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1529" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1530" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1531" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1522" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1522" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1522" s="5" t="s">
+        <v>3287</v>
+      </c>
+      <c r="C1522">
+        <v>1</v>
+      </c>
+      <c r="D1522" t="s">
+        <v>3279</v>
+      </c>
+      <c r="E1522">
+        <v>48</v>
+      </c>
+      <c r="F1522" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="G1522" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1523" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1523" s="5" t="s">
+        <v>3288</v>
+      </c>
+      <c r="C1523">
+        <v>1</v>
+      </c>
+      <c r="D1523" t="s">
+        <v>3280</v>
+      </c>
+      <c r="E1523">
+        <v>48</v>
+      </c>
+      <c r="F1523" s="3" t="s">
+        <v>3295</v>
+      </c>
+      <c r="G1523" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1524" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1524" s="5" t="s">
+        <v>3289</v>
+      </c>
+      <c r="C1524">
+        <v>1</v>
+      </c>
+      <c r="D1524" t="s">
+        <v>3281</v>
+      </c>
+      <c r="E1524">
+        <v>48</v>
+      </c>
+      <c r="F1524" s="3" t="s">
+        <v>3112</v>
+      </c>
+      <c r="G1524" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1525" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1525" s="5" t="s">
+        <v>3290</v>
+      </c>
+      <c r="C1525">
+        <v>1</v>
+      </c>
+      <c r="D1525" t="s">
+        <v>3282</v>
+      </c>
+      <c r="E1525">
+        <v>48</v>
+      </c>
+      <c r="F1525" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1525" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1526" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1526" s="5" t="s">
+        <v>3291</v>
+      </c>
+      <c r="C1526">
+        <v>1</v>
+      </c>
+      <c r="D1526" t="s">
+        <v>3283</v>
+      </c>
+      <c r="E1526">
+        <v>48</v>
+      </c>
+      <c r="F1526" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="G1526" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1527" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1527" s="5" t="s">
+        <v>3292</v>
+      </c>
+      <c r="C1527">
+        <v>1</v>
+      </c>
+      <c r="D1527" t="s">
+        <v>3284</v>
+      </c>
+      <c r="E1527">
+        <v>48</v>
+      </c>
+      <c r="F1527" s="3" t="s">
+        <v>3110</v>
+      </c>
+      <c r="G1527" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1528" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1528" s="5" t="s">
+        <v>3293</v>
+      </c>
+      <c r="C1528">
+        <v>1</v>
+      </c>
+      <c r="D1528" t="s">
+        <v>3285</v>
+      </c>
+      <c r="E1528">
+        <v>48</v>
+      </c>
+      <c r="F1528" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G1528" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1529" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1529" s="5" t="s">
+        <v>3294</v>
+      </c>
+      <c r="C1529">
+        <v>1</v>
+      </c>
+      <c r="D1529" t="s">
+        <v>3286</v>
+      </c>
+      <c r="E1529">
+        <v>96</v>
+      </c>
+      <c r="F1529" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1529" t="s">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1530"/>
+    </row>
+    <row r="1531" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1531"/>
+    </row>
     <row r="1532" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1533" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1534" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -48314,13 +48595,13 @@
     <row r="4027" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4028" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4029" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4030" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4031" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4032" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4033" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <conditionalFormatting sqref="B2:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="B1532:B1048576 B2:B1529">
+    <cfRule type="duplicateValues" dxfId="2" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
